--- a/data/export/2026-10-08-operations.xlsx
+++ b/data/export/2026-10-08-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1515,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,25 +2506,25 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2494,49 +2534,45 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2560,17 +2596,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2580,45 +2616,41 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2651,12 +2683,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2670,7 +2702,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2706,35 +2738,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2767,12 +2799,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2883,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,7 +2970,3603 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-operations.xlsx
+++ b/data/export/2026-10-08-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1131,36 +1139,32 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1168,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1192,37 +1196,33 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1316,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1412,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1443,7 +1451,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1454,7 +1462,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1495,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -1520,7 +1532,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1556,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1691,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1686,7 +1702,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1735,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1796,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1942,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2008,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2062,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2128,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2178,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2244,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2294,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2360,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2409,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2427,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2480,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2494,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2524,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2595,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2614,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2639,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2715,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2734,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,7 +2759,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2738,35 +2770,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2831,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2850,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2886,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2947,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2966,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +2991,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3067,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3086,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,7 +3111,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3086,35 +3122,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3183,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3202,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,46 +3227,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3303,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3322,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,7 +3347,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3318,35 +3358,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3419,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3438,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,18 +3463,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3491,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,7 +3501,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3467,40 +3511,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3562,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,33 +3572,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3615,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3573,7 +3625,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3583,40 +3635,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3696,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3739,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3689,7 +3749,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3699,40 +3759,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3810,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3820,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3840,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3863,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3873,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3843,12 +3911,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3930,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3887,7 +3955,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3898,7 +3966,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3979,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq30推进至seq34，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4027,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4040,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq28映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4094,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4107,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4155,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4174,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4210,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4143,22 +4223,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:26</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4191,12 +4271,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4290,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4326,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4339,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4349,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4387,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4406,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4442,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4455,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4423,12 +4503,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4522,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4558,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4571,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4539,12 +4619,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4638,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4674,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4687,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4617,7 +4697,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4655,12 +4735,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4754,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,35 +4790,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4851,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4870,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4815,7 +4895,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4826,35 +4906,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4967,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +4986,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4942,35 +5022,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5083,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5102,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5138,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5199,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5218,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5254,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5315,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5334,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5370,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5431,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5450,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5486,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5547,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5566,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5602,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5663,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5682,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5718,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5779,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5798,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5834,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5895,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5914,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5950,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6011,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6030,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6066,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6127,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6146,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6182,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6243,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6262,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6298,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6359,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6378,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6414,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6475,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6494,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6530,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6511,12 +6591,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6610,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6555,7 +6635,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6566,7 +6646,3299 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-operations.xlsx
+++ b/data/export/2026-10-08-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1505,24 +1505,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1619,32 +1619,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1652,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1676,17 +1680,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1696,13 +1700,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1745,24 +1753,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1772,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1821,12 +1829,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1900,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1931,7 +1939,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1975,32 +1983,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2008,7 +2020,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2032,37 +2044,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2095,32 +2107,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2128,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2152,33 +2168,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2211,32 +2231,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2244,7 +2268,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2268,33 +2292,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2327,32 +2355,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2360,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2384,32 +2416,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2447,32 +2479,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2480,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2504,17 +2540,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2524,12 +2560,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2600,7 +2636,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2639,7 +2675,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2654,7 +2690,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2836,7 +2872,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2952,7 +2988,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3006,7 +3042,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3108,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3188,7 +3224,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3237,12 +3273,12 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3344,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3352,13 +3388,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3464,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3473,82 +3513,78 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3562,7 +3598,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3572,17 +3608,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3592,87 +3628,79 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3686,7 +3714,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3696,107 +3724,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3810,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3820,65 +3844,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3911,12 +3935,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3930,7 +3954,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3960,51 +3984,55 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq30推进至seq34，推进4站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4027,12 +4055,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4040,25 +4068,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq28映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4083,46 +4099,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4155,12 +4175,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4174,7 +4194,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4199,18 +4219,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4223,52 +4247,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4276,7 +4304,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4290,7 +4318,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4300,33 +4328,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4371,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4349,7 +4381,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4359,40 +4391,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4406,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4416,33 +4452,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4495,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4465,7 +4505,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4475,40 +4515,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4522,7 +4566,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4532,33 +4576,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4619,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4581,7 +4629,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4619,12 +4667,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4638,7 +4686,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4663,7 +4711,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4687,7 +4735,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4697,7 +4745,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4707,12 +4755,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq30推进至seq59，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4735,12 +4783,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4748,13 +4796,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq28映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4779,7 +4839,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4803,60 +4863,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4870,7 +4934,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4880,33 +4944,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4987,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4929,7 +4997,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4939,40 +5007,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4986,7 +5058,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4996,33 +5068,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5111,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5045,7 +5121,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5083,12 +5159,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5102,7 +5178,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5127,7 +5203,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5151,7 +5227,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5161,7 +5237,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5199,12 +5275,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5218,7 +5294,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5243,7 +5319,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5267,7 +5343,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5277,7 +5353,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5315,12 +5391,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5334,7 +5410,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5383,22 +5459,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5431,12 +5507,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5450,7 +5526,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5499,32 +5575,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5547,12 +5623,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5560,13 +5636,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5615,22 +5707,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5663,12 +5755,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5682,7 +5774,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5731,7 +5823,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5741,7 +5833,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5751,12 +5843,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq44推进至seq47，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5779,12 +5871,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5792,13 +5884,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5847,22 +5951,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5895,12 +5999,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5914,7 +6018,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5963,22 +6067,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6011,12 +6115,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6030,7 +6134,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6079,7 +6183,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6089,7 +6193,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6127,12 +6231,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6146,7 +6250,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6195,7 +6299,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6205,7 +6309,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6243,12 +6347,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6262,7 +6366,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6311,22 +6415,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6359,12 +6463,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6378,7 +6482,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6427,22 +6531,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6475,12 +6579,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6494,7 +6598,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6543,7 +6647,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6553,7 +6657,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6591,12 +6695,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6610,7 +6714,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6659,7 +6763,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6669,7 +6773,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6707,12 +6811,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6726,7 +6830,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6751,22 +6855,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6879,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6789,7 +6889,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6827,12 +6927,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6846,7 +6946,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6871,22 +6971,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6995,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6909,7 +7005,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6952,7 +7048,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6966,7 +7062,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6991,7 +7087,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7009,28 +7105,28 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7063,12 +7159,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7082,7 +7178,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7107,7 +7203,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7118,35 +7214,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7179,12 +7275,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7198,7 +7294,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7223,7 +7319,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7234,35 +7330,35 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7295,12 +7391,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7314,7 +7410,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7339,7 +7435,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7350,77 +7446,73 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7434,7 +7526,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7444,17 +7536,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7469,40 +7561,40 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7535,12 +7627,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7554,7 +7646,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7579,88 +7671,88 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7674,7 +7766,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7684,17 +7776,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7704,87 +7796,79 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7798,7 +7882,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7808,17 +7892,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7833,40 +7917,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7899,12 +7983,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7918,7 +8002,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7943,7 +8027,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7954,35 +8038,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8015,12 +8099,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8034,7 +8118,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8059,46 +8143,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8131,12 +8219,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8150,7 +8238,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8180,41 +8268,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8247,12 +8339,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8266,7 +8358,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8291,7 +8383,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8302,35 +8394,35 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8363,12 +8455,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8382,7 +8474,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8407,7 +8499,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8418,7 +8510,7 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8523,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8441,7 +8533,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8484,7 +8576,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8498,7 +8590,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8523,18 +8615,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8643,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8557,7 +8653,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8595,12 +8691,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8614,7 +8710,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8639,7 +8735,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8663,22 +8759,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8716,7 +8812,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8730,7 +8826,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8755,7 +8851,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8779,7 +8875,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8789,7 +8885,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8799,40 +8895,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8846,7 +8946,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8856,17 +8956,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8876,13 +8976,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8999,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8905,7 +9009,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8915,32 +9019,36 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8948,7 +9056,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8962,7 +9070,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8972,33 +9080,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9011,60 +9123,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9078,7 +9194,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9088,33 +9204,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9247,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9137,7 +9257,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9147,40 +9267,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9194,7 +9318,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9204,17 +9328,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9224,13 +9348,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9371,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9253,7 +9381,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9296,7 +9424,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9310,7 +9438,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9340,17 +9468,13 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9363,60 +9487,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9430,7 +9558,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9440,33 +9568,37 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9479,60 +9611,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9546,7 +9682,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9556,17 +9692,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9581,12 +9717,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9599,60 +9735,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9666,7 +9806,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9676,17 +9816,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9696,13 +9836,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9715,60 +9859,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9782,7 +9930,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9792,17 +9940,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9817,12 +9965,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9983,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9845,7 +9993,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9855,40 +10003,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9902,41 +10054,2649 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-08-operations.xlsx
+++ b/data/export/2026-10-08-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5172,17 +5172,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,17 +8272,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8764,17 +8764,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10252,17 +10252,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10748,17 +10748,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11659,32 +11659,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11692,7 +11696,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11716,17 +11720,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11736,17 +11740,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11783,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11812,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11836,17 +11844,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11856,17 +11864,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11899,32 +11907,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11932,7 +11944,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11956,17 +11968,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11976,17 +11988,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12019,32 +12031,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12052,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12076,17 +12092,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12096,12 +12112,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12139,32 +12155,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12172,7 +12192,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12196,17 +12216,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12216,12 +12236,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12292,7 +12312,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12341,7 +12361,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12412,7 +12432,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12456,17 +12476,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12556,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12580,17 +12600,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12734,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12804,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12838,7 +12858,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13230,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13354,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13548,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13652,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13696,17 +13716,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14048,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14072,17 +14092,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14168,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14284,7 +14304,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14338,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14428,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14452,12 +14472,12 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
@@ -14532,7 +14552,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14576,17 +14596,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14730,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14800,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14904,7 +14924,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14958,7 +14978,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15044,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15264,7 +15284,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15318,7 +15338,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15462,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15532,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15556,17 +15576,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -15686,7 +15706,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15772,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15806,7 +15826,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15950,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16000,7 +16020,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16044,17 +16064,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -16244,7 +16264,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16298,7 +16318,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16550,7 +16570,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -16674,7 +16694,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16868,7 +16888,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16992,7 +17012,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17036,17 +17056,17 @@
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17136,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17160,17 +17180,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17384,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17408,12 +17428,12 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -17488,7 +17508,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17542,7 +17562,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17632,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17656,17 +17676,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17790,7 +17810,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17860,7 +17880,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17984,7 +18004,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18038,7 +18058,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -18162,7 +18182,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18252,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18286,7 +18306,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -18410,7 +18430,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18500,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18534,7 +18554,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18802,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -18848,7 +18868,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -19108,7 +19128,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19232,7 +19252,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19410,7 +19430,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -19480,7 +19500,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19524,12 +19544,12 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
@@ -19658,7 +19678,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -19728,7 +19748,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19782,7 +19802,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -19906,7 +19926,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -20278,7 +20298,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -20526,7 +20546,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20616,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20640,17 +20660,17 @@
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20872,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20896,17 +20916,17 @@
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20976,7 +20996,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21096,7 +21116,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21216,7 +21236,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21260,17 +21280,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21360,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21384,17 +21404,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -21464,7 +21484,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21518,7 +21538,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21604,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21628,17 +21648,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -21708,7 +21728,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21762,7 +21782,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21852,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21956,7 +21976,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22010,7 +22030,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22204,7 +22224,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22258,7 +22278,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22402,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22506,7 +22526,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -22630,7 +22650,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22754,7 +22774,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -22878,7 +22898,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23088,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23177,12 +23197,12 @@
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O184" s="2" t="inlineStr">
@@ -23192,7 +23212,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23279,32 +23299,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23312,7 +23336,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23336,17 +23360,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23356,12 +23380,12 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
@@ -23399,32 +23423,36 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23432,7 +23460,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23456,17 +23484,17 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA186" s="2" t="inlineStr">
@@ -23476,17 +23504,17 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -23519,32 +23547,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23552,7 +23584,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23576,17 +23608,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23596,17 +23628,17 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23639,12 +23671,12 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq30推进至seq60，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -23672,7 +23704,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23680,10 +23712,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R188" s="2" t="inlineStr"/>
-      <c r="S188" s="2" t="inlineStr"/>
-      <c r="T188" s="2" t="inlineStr"/>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq30（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="V188" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -23726,7 +23774,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -23759,32 +23807,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23792,7 +23844,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23816,17 +23868,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23836,17 +23888,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23879,32 +23931,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23912,7 +23968,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23936,17 +23992,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23956,17 +24012,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -24032,7 +24088,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24119,12 +24175,12 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -24152,7 +24208,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24160,10 +24216,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24206,7 +24278,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -24272,7 +24344,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24326,7 +24398,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24359,32 +24431,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24392,7 +24468,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24416,17 +24492,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24436,17 +24512,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24588,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24566,7 +24642,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24632,7 +24708,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24752,7 +24828,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24806,7 +24882,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24872,7 +24948,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24992,7 +25068,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25036,17 +25112,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -25480,7 +25556,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25524,17 +25600,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -25604,7 +25680,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25972,7 +26048,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26021,12 +26097,12 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26172,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26140,17 +26216,17 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26398,7 +26474,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26646,7 +26722,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26766,7 +26842,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26836,7 +26912,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26880,17 +26956,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26960,7 +27036,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27004,17 +27080,17 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27448,7 +27524,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27750,7 +27826,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27944,7 +28020,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27988,17 +28064,17 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28188,7 +28264,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28232,17 +28308,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28312,7 +28388,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28361,12 +28437,12 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28686,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28854,7 +28930,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28924,7 +29000,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28968,17 +29044,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29292,7 +29368,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29672,7 +29748,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29728,17 +29804,17 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29986,7 +30062,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30234,7 +30310,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31102,7 +31178,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31350,7 +31426,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32040,7 +32116,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32084,17 +32160,17 @@
       </c>
       <c r="AB256" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC256" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32342,7 +32418,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32536,7 +32612,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32580,17 +32656,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32714,7 +32790,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32838,7 +32914,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32908,7 +32984,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32957,12 +33033,12 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33352,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33400,7 +33476,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33444,17 +33520,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33648,7 +33724,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33692,17 +33768,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34144,7 +34220,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34188,17 +34264,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34322,7 +34398,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34694,7 +34770,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34764,7 +34840,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34808,17 +34884,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34942,7 +35018,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35012,7 +35088,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35061,12 +35137,12 @@
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35376,7 +35452,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35496,7 +35572,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35540,17 +35616,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35944,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35912,17 +35988,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36290,7 +36366,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36360,7 +36436,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36404,17 +36480,17 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36538,7 +36614,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36856,7 +36932,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36900,17 +36976,17 @@
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC295" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36965,12 +37041,12 @@
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O296" s="2" t="inlineStr">
@@ -36980,7 +37056,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37077,24 +37153,24 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O297" s="2" t="inlineStr">
@@ -37104,7 +37180,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37153,12 +37229,12 @@
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37191,32 +37267,36 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N298" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O298" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37224,7 +37304,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37248,17 +37328,17 @@
       </c>
       <c r="X298" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA298" s="2" t="inlineStr">
@@ -37268,17 +37348,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37311,32 +37391,36 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N299" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O299" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37344,7 +37428,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37368,17 +37452,17 @@
       </c>
       <c r="X299" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA299" s="2" t="inlineStr">
@@ -37388,17 +37472,17 @@
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37431,32 +37515,36 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O300" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -37464,7 +37552,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37488,17 +37576,17 @@
       </c>
       <c r="X300" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA300" s="2" t="inlineStr">
@@ -37508,17 +37596,17 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37551,32 +37639,36 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N301" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37584,7 +37676,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37608,17 +37700,17 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA301" s="2" t="inlineStr">
@@ -37628,17 +37720,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37704,7 +37796,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37753,12 +37845,12 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37824,7 +37916,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37868,17 +37960,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
